--- a/data/trans_orig/ProbViv_estruc-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/ProbViv_estruc-Habitat-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9024</t>
+          <t>9154</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21175</t>
+          <t>21470</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4298</t>
+          <t>4316</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14213</t>
+          <t>14372</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15742</t>
+          <t>15812</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>31217</t>
+          <t>31675</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,29%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>96105</t>
+          <t>95810</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>108256</t>
+          <t>108126</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>81,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>126199</t>
+          <t>126040</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>136114</t>
+          <t>136096</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>226476</t>
+          <t>226018</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>241951</t>
+          <t>241881</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,86%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8184</t>
+          <t>7876</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18831</t>
+          <t>18609</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18260</t>
+          <t>17088</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>35881</t>
+          <t>35434</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28578</t>
+          <t>28405</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>49353</t>
+          <t>48548</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>10,92%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>170682</t>
+          <t>170904</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>181329</t>
+          <t>181637</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>219154</t>
+          <t>219601</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>236775</t>
+          <t>237947</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>395195</t>
+          <t>396000</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>415970</t>
+          <t>416143</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>89,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,61%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10078</t>
+          <t>10291</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29237</t>
+          <t>29548</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10052</t>
+          <t>10777</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25274</t>
+          <t>26007</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23832</t>
+          <t>25410</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>48886</t>
+          <t>50676</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,49%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>161164</t>
+          <t>160853</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>180323</t>
+          <t>180110</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,64%</t>
+          <t>84,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>160012</t>
+          <t>159279</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>175234</t>
+          <t>174509</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>85,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>326801</t>
+          <t>325011</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>351855</t>
+          <t>350277</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,24%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12486</t>
+          <t>13313</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29798</t>
+          <t>30480</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15128</t>
+          <t>15673</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30597</t>
+          <t>30723</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>33203</t>
+          <t>31173</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>55123</t>
+          <t>54220</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,57%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>138164</t>
+          <t>137482</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>155476</t>
+          <t>154649</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>81,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>149698</t>
+          <t>149572</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>165167</t>
+          <t>164622</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>82,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>293134</t>
+          <t>294037</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>315054</t>
+          <t>317084</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,17%</t>
+          <t>84,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>91,05%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>51383</t>
+          <t>50689</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>83388</t>
+          <t>81698</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>59503</t>
+          <t>58030</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>88982</t>
+          <t>90503</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>117506</t>
+          <t>117272</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>160601</t>
+          <t>159766</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,2%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>581768</t>
+          <t>583458</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>613773</t>
+          <t>614467</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>672046</t>
+          <t>670525</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>701525</t>
+          <t>702998</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1265583</t>
+          <t>1266418</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1308678</t>
+          <t>1308912</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,78%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/ProbViv_estruc-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/ProbViv_estruc-Habitat-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7600</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3761</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>12923</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>6,04%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2,99%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>10,26%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>14049</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>9154</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>21470</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>11,98%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>7,81%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>18,31%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>8440</t>
+          <t>15453</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4316</t>
+          <t>9636</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14372</t>
+          <t>24664</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>22489</t>
+          <t>23053</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15812</t>
+          <t>15279</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>31675</t>
+          <t>33195</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>13,44%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>118306</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>112983</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>122145</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>93,96%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>89,74%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>97,01%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>174</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>103231</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>95810</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>108126</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>88,02%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>81,69%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>92,19%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>131972</t>
+          <t>105618</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>126040</t>
+          <t>96407</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>136096</t>
+          <t>111435</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>79,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>235204</t>
+          <t>223924</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>226018</t>
+          <t>213782</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>241881</t>
+          <t>231698</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>86,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,81%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>196</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>24721</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>17807</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>35771</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>10,42%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>7,51%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>15,08%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>12550</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>7876</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>18609</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>6,62%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>4,16%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>9,82%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>25219</t>
+          <t>12613</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17088</t>
+          <t>8284</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>35434</t>
+          <t>19072</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>37768</t>
+          <t>37335</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28405</t>
+          <t>28084</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>48548</t>
+          <t>48107</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,44%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>212485</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>201435</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>219399</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>89,58%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>84,92%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>92,49%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>255</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>176963</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>170904</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>181637</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>93,38%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>90,18%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>95,84%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>229816</t>
+          <t>170724</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>219601</t>
+          <t>164265</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>237947</t>
+          <t>175053</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>89,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>406780</t>
+          <t>383208</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>396000</t>
+          <t>372436</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>416143</t>
+          <t>392459</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>88,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,32%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>343</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>279</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>189513</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>189513</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>189513</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>343</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>183337</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>183337</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>183337</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>444548</t>
+          <t>420543</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>444548</t>
+          <t>420543</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>444548</t>
+          <t>420543</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>14941</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9100</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>23052</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>8,88%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>5,41%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>13,69%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>18218</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>10291</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>29548</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>9,57%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5,4%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>15,52%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>17249</t>
+          <t>15454</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10777</t>
+          <t>9713</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26007</t>
+          <t>21829</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>35467</t>
+          <t>30394</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>25410</t>
+          <t>22062</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>50676</t>
+          <t>41102</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>12,63%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>153400</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>145289</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>159241</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>91,12%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>86,31%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>94,59%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>204</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>172183</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>160853</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>180110</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>90,43%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>84,48%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>94,6%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>203</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>168037</t>
+          <t>141596</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>159279</t>
+          <t>135221</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>174509</t>
+          <t>147337</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>86,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>340220</t>
+          <t>294997</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>325011</t>
+          <t>284289</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>350277</t>
+          <t>303329</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,22%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>227</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>190401</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>190401</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>190401</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>157050</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>157050</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>157050</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>375687</t>
+          <t>325391</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>375687</t>
+          <t>325391</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>375687</t>
+          <t>325391</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>20922</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>14254</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>29402</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>12,42%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>8,46%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>17,46%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>19988</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>13313</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>30480</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>11,9%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>7,93%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>18,15%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>22422</t>
+          <t>17836</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15673</t>
+          <t>11735</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30723</t>
+          <t>25690</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>42410</t>
+          <t>38758</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>31173</t>
+          <t>29431</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>54220</t>
+          <t>49605</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>14,78%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>147497</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>139017</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>154165</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>87,58%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>82,54%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>91,54%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>215</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>147974</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>137482</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>154649</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>88,1%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>81,85%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>92,07%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>157873</t>
+          <t>149309</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>149572</t>
+          <t>141455</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>164622</t>
+          <t>155410</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,96%</t>
+          <t>84,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>305847</t>
+          <t>296806</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>294037</t>
+          <t>285959</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>317084</t>
+          <t>306133</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>88,45%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>85,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>91,23%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>240</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>180295</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>180295</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>180295</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>348257</t>
+          <t>335564</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>348257</t>
+          <t>335564</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>348257</t>
+          <t>335564</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>68184</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>54905</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>83074</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>9,74%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>7,84%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>11,87%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>64805</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>50689</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>81698</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>9,74%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>7,62%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>12,28%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>73329</t>
+          <t>61356</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>58030</t>
+          <t>49795</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>90503</t>
+          <t>75604</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>138135</t>
+          <t>129540</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>117272</t>
+          <t>112229</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>159766</t>
+          <t>148939</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,21%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>877</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>631688</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>616798</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>644967</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>90,26%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>88,13%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>92,16%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>848</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>600351</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>583458</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>614467</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>90,26%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>87,72%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>92,38%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>877</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>687699</t>
+          <t>567247</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>670525</t>
+          <t>552999</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>702998</t>
+          <t>578808</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1288049</t>
+          <t>1198935</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1266418</t>
+          <t>1179536</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1308912</t>
+          <t>1216246</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,55%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>699872</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>699872</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>699872</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>942</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>665156</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>665156</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>665156</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>976</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>761028</t>
+          <t>628603</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>761028</t>
+          <t>628603</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>761028</t>
+          <t>628603</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1426184</t>
+          <t>1328475</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1426184</t>
+          <t>1328475</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1426184</t>
+          <t>1328475</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
